--- a/tests/MarkView_手動テスト仕様書.xlsx
+++ b/tests/MarkView_手動テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\repos\go_MarkView\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B97388B7-5022-4158-88CB-F8408D80D5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57A893B0-144D-4F1A-987A-40613AFEEF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="15345" xr2:uid="{FEF1CFF5-9A85-4F0B-B60A-9AEE72F02837}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="15345" xr2:uid="{C867D9F0-26B0-454D-8727-77664267F6D1}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="3" r:id="rId1"/>
@@ -357,7 +357,7 @@
   </si>
   <si>
     <t>1. ツールバー左端のフォルダアイコンをクリックする
-2. testdata/e2e/showcase.md を選択して開く</t>
+2. testdata/showcase.md を選択して開く</t>
   </si>
   <si>
     <t>・OS 標準のファイル選択ダイアログが開く
@@ -1961,7 +1961,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72EDE0B5-ED45-4449-9B4A-E2DCB8A89EBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFCC152-243C-4D55-9F13-D6C0C7CBD85C}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -2108,7 +2108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4230C645-3580-4C03-8492-ED941AD15F48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6FFB79D-20D2-4057-9155-A0046B9FD488}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4422,10 +4422,10 @@
       <c r="P60" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{4230C645-3580-4C03-8492-ED941AD15F48}"/>
+  <autoFilter ref="A1:P1" xr:uid="{E6FFB79D-20D2-4057-9155-A0046B9FD488}"/>
   <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N60" xr:uid="{62028560-6994-4238-88D9-4405654D7A1C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N60" xr:uid="{4AD97EA7-76C0-44EB-BB32-C64264869365}">
       <formula1>"OK,NG,対象外,未実施"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4435,7 +4435,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5163C89-8E4E-45BE-84AA-DED177C7508E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC07FB5-4A23-4CD7-A474-2FA76133704F}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
